--- a/DATA/MODELADO/Diagnosticos/Exp01-V3/recomendaciones_Exp01-V3.xlsx
+++ b/DATA/MODELADO/Diagnosticos/Exp01-V3/recomendaciones_Exp01-V3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,33 +438,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>• Optimizar la sensibilidad del modelo para mejorar la detección de eventos IRCA.</t>
+          <t>• El conjunto presenta desbalance de clases; aplicar técnicas de balanceo antes del entrenamiento.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>• El conjunto presenta desbalance de clases; utilizar técnicas de balanceo antes del entrenamiento.</t>
+          <t>• Comparar el desempeño del modelo LSTM con Random Forest, XGBoost y Redes Dense.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>• Comparar el desempeño del modelo LSTM con Random Forest, XGBoost y Redes Dense.</t>
+          <t>• Evaluar el modelo utilizando validación cruzada temporal.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
-        <is>
-          <t>• Evaluar el modelo utilizando validación cruzada temporal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
         <is>
           <t>• Documentar todos los experimentos para garantizar la reproducibilidad.</t>
         </is>
